--- a/addons/project/static/xls/tasks_import_template.xlsx
+++ b/addons/project/static/xls/tasks_import_template.xlsx
@@ -22,7 +22,7 @@
     <t>Project*</t>
   </si>
   <si>
-    <t>Stage</t>
+    <t>Workflow Step</t>
   </si>
   <si>
     <t>State*</t>
@@ -64,10 +64,10 @@
     <t>In Progress</t>
   </si>
   <si>
-    <t>Deco Addict</t>
-  </si>
-  <si>
-    <t>Medium priority</t>
+    <t>Acme Corporation</t>
+  </si>
+  <si>
+    <t>Important</t>
   </si>
   <si>
     <t>Meeting</t>
